--- a/experiment/HAT_2CH_bestx4/Test/results_table_HAT_2CH.xlsx
+++ b/experiment/HAT_2CH_bestx4/Test/results_table_HAT_2CH.xlsx
@@ -570,37 +570,37 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>32.214/
-0.8937</t>
+          <t>32.236/
+0.8939</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.660/
-0.7833</t>
+          <t>28.662/
+0.7832</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.613/
+          <t>27.619/
 0.7385</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>26.156/
-0.7886</t>
+          <t>26.166/
+0.7887</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>30.597/
+          <t>30.587/
 0.9104</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>29.048/
+          <t>29.054/
 0.8229</t>
         </is>
       </c>
